--- a/diseases/d163/2005-2009.xlsx
+++ b/diseases/d163/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>6</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.1297823722660262</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.1081519768883552</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1730431630213682</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.1081519768883552</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.1081519768883552</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>6</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.1297823722660262</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>9</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.1946735583990393</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>6</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.1297823722660262</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>5</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.1072847642331478</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>3</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.06437085853988869</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -6853,9 +6808,6 @@
       <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.06437085853988869</v>
       </c>
@@ -7397,9 +7349,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -7941,9 +7890,6 @@
       <c r="O39" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -8337,9 +8283,6 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -8733,9 +8676,6 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -9129,9 +9069,6 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -9525,9 +9462,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9921,9 +9855,6 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -10317,9 +10248,6 @@
       <c r="O51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.06437085853988869</v>
       </c>
@@ -10713,9 +10641,6 @@
       <c r="O53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -11109,9 +11034,6 @@
       <c r="O55" t="n">
         <v>3</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.06370765829760396</v>
       </c>
@@ -11505,9 +11427,6 @@
       <c r="O57" t="n">
         <v>6</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.1274153165952079</v>
       </c>
@@ -11901,9 +11820,6 @@
       <c r="O59" t="n">
         <v>2</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -12297,9 +12213,6 @@
       <c r="O61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -12693,9 +12606,6 @@
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -13089,9 +12999,6 @@
       <c r="O65" t="n">
         <v>3</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.06370765829760396</v>
       </c>
@@ -13485,9 +13392,6 @@
       <c r="O67" t="n">
         <v>9</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1911229748928119</v>
       </c>
@@ -13881,9 +13785,6 @@
       <c r="O69" t="n">
         <v>7</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.1486512026944092</v>
       </c>
@@ -14277,9 +14178,6 @@
       <c r="O71" t="n">
         <v>15</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.3185382914880198</v>
       </c>
@@ -14673,9 +14571,6 @@
       <c r="O73" t="n">
         <v>14</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.2973024053888185</v>
       </c>
@@ -15069,9 +14964,6 @@
       <c r="O75" t="n">
         <v>12</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.2548306331904158</v>
       </c>
@@ -15613,9 +15505,6 @@
       <c r="O78" t="n">
         <v>4</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -16009,9 +15898,6 @@
       <c r="O80" t="n">
         <v>12</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.251672521198691</v>
       </c>
@@ -16405,9 +16291,6 @@
       <c r="O82" t="n">
         <v>6</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.1258362605993455</v>
       </c>
@@ -16949,9 +16832,6 @@
       <c r="O85" t="n">
         <v>3</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.06291813029967276</v>
       </c>
@@ -17345,9 +17225,6 @@
       <c r="O87" t="n">
         <v>7</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.1468089706992364</v>
       </c>
@@ -17741,9 +17618,6 @@
       <c r="O89" t="n">
         <v>2</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -18137,9 +18011,6 @@
       <c r="O91" t="n">
         <v>4</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -18533,9 +18404,6 @@
       <c r="O93" t="n">
         <v>5</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -18929,9 +18797,6 @@
       <c r="O95" t="n">
         <v>2</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -19325,9 +19190,6 @@
       <c r="O97" t="n">
         <v>3</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.06291813029967276</v>
       </c>
@@ -19721,9 +19583,6 @@
       <c r="O99" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -20117,9 +19976,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -20513,9 +20369,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -20909,9 +20762,6 @@
       <c r="O105" t="n">
         <v>3</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -21305,9 +21155,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -21701,9 +21548,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -22097,9 +21941,6 @@
       <c r="O111" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -22493,9 +22334,6 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -22889,9 +22727,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -23285,9 +23120,6 @@
       <c r="O117" t="n">
         <v>2</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -23681,9 +23513,6 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -24077,9 +23906,6 @@
       <c r="O121" t="n">
         <v>2</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -24473,9 +24299,6 @@
       <c r="O123" t="n">
         <v>2</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -24868,9 +24691,6 @@
       </c>
       <c r="O125" t="n">
         <v>3</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0.06212952037563508</v>
